--- a/LISTAS_ORDENADAS/MI/Tornillos Pitones Arandelas Tuercas/PITONES.xlsx
+++ b/LISTAS_ORDENADAS/MI/Tornillos Pitones Arandelas Tuercas/PITONES.xlsx
@@ -829,7 +829,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45208.55638223072</v>
+        <v>45266</v>
       </c>
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
@@ -939,25 +939,6 @@
       <c r="F10" s="15" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30" ht="27" customHeight="1" s="30">
       <c r="A30" s="29" t="inlineStr">
         <is>
@@ -1080,7 +1061,6 @@
       </c>
       <c r="N37" s="20" t="n"/>
     </row>
-    <row r="38"/>
     <row r="39" ht="26.25" customHeight="1" s="30">
       <c r="A39" s="28" t="inlineStr">
         <is>
@@ -1185,13 +1165,6 @@
         <v>2437.246</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -1201,10 +1174,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A30:F30"/>
     <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
